--- a/config/new-five-tables/source/03_TCIM_十题_证据命题来源等级与反事实判据表_V0.2.1_唯一运行版.xlsx
+++ b/config/new-five-tables/source/03_TCIM_十题_证据命题来源等级与反事实判据表_V0.2.1_唯一运行版.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Ra7bbc6c89ba64dee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RUNTIME_CONTRACT" sheetId="2" r:id="R1eb3858f4402410a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QUESTION_INDEX" sheetId="3" r:id="Rc50cefb76b5b42bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DATA" sheetId="4" r:id="R0edfaaa74ac44db0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DICTIONARY" sheetId="5" r:id="R9d0380c8a17f491e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENUMS" sheetId="6" r:id="R8a1159fa69b443fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA_SUMMARY" sheetId="7" r:id="R3a252cb9fd944c05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHANGELOG" sheetId="8" r:id="R55de60a506304c81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R4f43d081d9a04876"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RUNTIME_CONTRACT" sheetId="2" r:id="R4d82a6b2b21249b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QUESTION_INDEX" sheetId="3" r:id="R7b73e5d433584206"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DATA" sheetId="4" r:id="Re7e47c2ec0d34994"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DICTIONARY" sheetId="5" r:id="R5fd7d7f111fc4b26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENUMS" sheetId="6" r:id="Rc63ed9e631fd4d1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA_SUMMARY" sheetId="7" r:id="R11afaddd58e94c41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHANGELOG" sheetId="8" r:id="R5fcee83613464401"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5983,7 +5983,7 @@
         <x:v>CAPABILITY_EVIDENCE</x:v>
       </x:c>
       <x:c r="H37" s="14" t="str">
-        <x:v>C01|C04|C08</x:v>
+        <x:v>C01|C04</x:v>
       </x:c>
       <x:c r="I37" s="14" t="str">
         <x:v>PATH-Q07-001-A|PATH-Q07-001-B|PATH-Q07-001-C</x:v>
@@ -6385,7 +6385,7 @@
         <x:v>CAPABILITY_EVIDENCE</x:v>
       </x:c>
       <x:c r="H40" s="14" t="str">
-        <x:v>C05|C06|C10</x:v>
+        <x:v>C05|C06|C10|C11</x:v>
       </x:c>
       <x:c r="I40" s="14" t="str">
         <x:v>PATH-Q07-004-A|PATH-Q07-004-B|PATH-Q07-004-C</x:v>
@@ -6519,16 +6519,16 @@
         <x:v>CAPABILITY_EVIDENCE</x:v>
       </x:c>
       <x:c r="H41" s="14" t="str">
-        <x:v>C08|C11</x:v>
+        <x:v>C07|C08</x:v>
       </x:c>
       <x:c r="I41" s="14" t="str">
         <x:v>PATH-Q07-005-A|PATH-Q07-005-B|PATH-Q07-005-C</x:v>
       </x:c>
       <x:c r="J41" s="14" t="str">
-        <x:v>教师能条件性平衡身体活动目标、自主选择和合理例外。</x:v>
+        <x:v>教师能通过包容性的材料、空间与角色配置，在尊重儿童自主选择和合理例外的同时持续提供可进入的身体活动机会。</x:v>
       </x:c>
       <x:c r="K41" s="14" t="str">
-        <x:v>说明个体差异和持续提供机会</x:v>
+        <x:v>说明个体差异，并把材料、空间或角色调整与持续参与机会相连。</x:v>
       </x:c>
       <x:c r="L41" s="14" t="str">
         <x:v>{"L0":"统一强制或完全不管。","L1":"承认两者重要但处理模糊。","L2":"通过兴趣化、多强度和不同进入时机实现目标。","L3":"考虑身体状态和个别例外，并持续提供可进入机会。"}</x:v>
@@ -6549,16 +6549,16 @@
         <x:v>L2</x:v>
       </x:c>
       <x:c r="R41" s="14" t="str">
-        <x:v>时间纪律高于儿童状态|以自主回避课程责任</x:v>
+        <x:v>用统一难度要求所有儿童|只允许旁观且不再提供可进入路径</x:v>
       </x:c>
       <x:c r="S41" s="14" t="str">
-        <x:v>抽象说“尊重又引导”</x:v>
+        <x:v>抽象说“尊重差异”但没有可进入的环境或角色安排</x:v>
       </x:c>
       <x:c r="T41" s="14" t="str">
-        <x:v>园所存在强制性活动要求</x:v>
+        <x:v>园所存在统一活动要求，但仍可通过强度、材料或角色作合理调整。</x:v>
       </x:c>
       <x:c r="U41" s="14" t="str">
-        <x:v>比较条件变化后判断是否随证据调整</x:v>
+        <x:v>询问教师会如何调整器材、空间、动作强度或角色，并依据什么判断调整有效。</x:v>
       </x:c>
       <x:c r="V41" s="14" t="str">
         <x:v>保留相互矛盾的原话与来源；标记CONFLICT，由后续证据修订，不静默覆盖。</x:v>
@@ -7189,7 +7189,7 @@
         <x:v>CAPABILITY_EVIDENCE</x:v>
       </x:c>
       <x:c r="H46" s="14" t="str">
-        <x:v>C07|C09</x:v>
+        <x:v>C07|C08|C11</x:v>
       </x:c>
       <x:c r="I46" s="14" t="str">
         <x:v>PATH-Q08-005-A|PATH-Q08-005-B|PATH-Q08-005-C</x:v>
@@ -7725,7 +7725,7 @@
         <x:v>CAPABILITY_EVIDENCE</x:v>
       </x:c>
       <x:c r="H50" s="14" t="str">
-        <x:v>C06|C10|C11</x:v>
+        <x:v>C06|C11</x:v>
       </x:c>
       <x:c r="I50" s="14" t="str">
         <x:v>PATH-Q09-004-A|PATH-Q09-004-B|PATH-Q09-004-C</x:v>
@@ -7859,7 +7859,7 @@
         <x:v>CAPABILITY_EVIDENCE</x:v>
       </x:c>
       <x:c r="H51" s="14" t="str">
-        <x:v>C07|C10</x:v>
+        <x:v>C07|C09|C10</x:v>
       </x:c>
       <x:c r="I51" s="14" t="str">
         <x:v>PATH-Q09-005-A|PATH-Q09-005-B|PATH-Q09-005-C</x:v>
@@ -8127,7 +8127,7 @@
         <x:v>CAPABILITY_EVIDENCE</x:v>
       </x:c>
       <x:c r="H53" s="14" t="str">
-        <x:v>C05|C10|C11</x:v>
+        <x:v>C05|C11</x:v>
       </x:c>
       <x:c r="I53" s="14" t="str">
         <x:v>PATH-Q10-002-A|PATH-Q10-002-B|PATH-Q10-002-C</x:v>
@@ -8261,7 +8261,7 @@
         <x:v>CAPABILITY_EVIDENCE</x:v>
       </x:c>
       <x:c r="H54" s="14" t="str">
-        <x:v>C06|C10|C11</x:v>
+        <x:v>C06|C11</x:v>
       </x:c>
       <x:c r="I54" s="14" t="str">
         <x:v>PATH-Q10-003-A|PATH-Q10-003-B|PATH-Q10-003-C</x:v>
@@ -8395,7 +8395,7 @@
         <x:v>CAPABILITY_EVIDENCE</x:v>
       </x:c>
       <x:c r="H55" s="14" t="str">
-        <x:v>C05|C10|C07|C08</x:v>
+        <x:v>C07|C08</x:v>
       </x:c>
       <x:c r="I55" s="14" t="str">
         <x:v>PATH-Q10-004-A|PATH-Q10-004-B|PATH-Q10-004-C</x:v>
@@ -8529,19 +8529,19 @@
         <x:v>CAPABILITY_EVIDENCE</x:v>
       </x:c>
       <x:c r="H56" s="14" t="str">
-        <x:v>C07|C09</x:v>
+        <x:v>C09|C10|C12</x:v>
       </x:c>
       <x:c r="I56" s="14" t="str">
         <x:v>PATH-Q10-005-A|PATH-Q10-005-B|PATH-Q10-005-C</x:v>
       </x:c>
       <x:c r="J56" s="14" t="str">
-        <x:v>教师能说明材料和空间调整的有限功能，并与规则、公平和后续观察联动。</x:v>
+        <x:v>教师能让幼儿依据规则试行后的安全、等待、公平和参与体验修正规则，并说明教师逐步退出的条件。</x:v>
       </x:c>
       <x:c r="K56" s="14" t="str">
-        <x:v>明确材料解决和不解决的问题</x:v>
+        <x:v>提出短时试行、反馈来源、修订办法和教师渐退条件。</x:v>
       </x:c>
       <x:c r="L56" s="14" t="str">
-        <x:v>{"L0":"只增加器材或扩大空间。","L1":"能减拥挤但不处理轮候。","L2":"材料空间与共同规则配套并说明边界。","L3":"依据新数据修订环境和规则，同时看安全、公平、参与。"}</x:v>
+        <x:v>{"L0":"只宣布成人规则，或笼统说“试试看”，没有反馈和修订机制。","L1":"提出试行或回顾，但未说明观察什么、由谁反馈或如何修订。","L2":"让幼儿依据至少一种可观察体验反馈并修订规则，说明教师何时减少控制。","L3":"综合安全、等待、公平和不同角色体验进行多轮试行修订，并建立儿童可继续自我治理的反馈办法。"}</x:v>
       </x:c>
       <x:c r="M56" s="14" t="str">
         <x:v>RO0|RO1|RO2|RO3|RO4</x:v>
@@ -8559,34 +8559,34 @@
         <x:v>L2</x:v>
       </x:c>
       <x:c r="R56" s="14" t="str">
-        <x:v>新增器材后更混乱仍不调整|材料替代共同治理</x:v>
+        <x:v>试行无论结果如何都不允许修改|教师始终掌握规则解释和执行权</x:v>
       </x:c>
       <x:c r="S56" s="14" t="str">
-        <x:v>器材越多越好|分区即解决公平</x:v>
+        <x:v>活动结束后教师单方面总结|把儿童同意成人方案当作共同治理</x:v>
       </x:c>
       <x:c r="T56" s="14" t="str">
-        <x:v>器材确为主要瓶颈|空间标识比器材数量更关键</x:v>
+        <x:v>短时访谈尚未展开完整试行流程，可进一步询问反馈和退出条件。</x:v>
       </x:c>
       <x:c r="U56" s="14" t="str">
-        <x:v>比较条件变化后判断是否随证据调整</x:v>
+        <x:v>请教师说明试行一轮后会听取谁的什么反馈、怎样修改，以及何时把执行权交回幼儿。</x:v>
       </x:c>
       <x:c r="V56" s="14" t="str">
-        <x:v>保留相互矛盾的原话与来源；标记CONFLICT，由后续证据修订，不静默覆盖。</x:v>
+        <x:v>若教师明确拒绝根据儿童体验修订规则，或把试行仅作为服从检验，则形成反证。</x:v>
       </x:c>
       <x:c r="W56" s="14" t="str">
-        <x:v>仅本题、本次叙述与明确相似情境</x:v>
+        <x:v>仅支持当前情境中的规则试行、反馈与渐退判断。</x:v>
       </x:c>
       <x:c r="X56" s="14" t="str">
-        <x:v>SITUATION_SPECIFIC_PATTERN</x:v>
+        <x:v>EPISODE_DESCRIPTION</x:v>
       </x:c>
       <x:c r="Y56" s="14" t="str">
-        <x:v>教师已具备稳定环境创设能力</x:v>
+        <x:v>不得由一次表述推断教师稳定具备班级自治或公平治理能力。</x:v>
       </x:c>
       <x:c r="Z56" s="14" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="AA56" s="14" t="str">
-        <x:v>短答、方言、文化礼貌、教龄和情境资源差异不得直接解释为能力不足。</x:v>
+        <x:v>不要求专业术语；能用日常语言说明反馈、修订和退出条件即可。</x:v>
       </x:c>
       <x:c r="AB56" s="26" t="b">
         <x:v>1</x:v>
@@ -8637,7 +8637,7 @@
         <x:v>同一能力下列出的A/B/C（或A/B）路径是可替代的实现路径；教师体现其中任意一条且满足证据锚点即可，不要求同时体现全部路径。 对应表2同题同能力路径组：PATH-Q10-005-A、PATH-Q10-005-B、PATH-Q10-005-C。</x:v>
       </x:c>
       <x:c r="AR56" s="11" t="str">
-        <x:v>C07</x:v>
+        <x:v>C09</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8681,7 +8681,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44a489ba752747a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R058d4d54c4b84d90"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10662,13 +10662,13 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
-        <x:v>表3能力引用存在</x:v>
+        <x:v>表3能力引用与所绑定表2路径的全局父级集合完全一致</x:v>
       </x:c>
       <x:c r="D13" s="14" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="E13" s="14" t="str">
-        <x:v>T3.capability_refs -&gt; T2.capability_concept_id</x:v>
+        <x:v>capability_refs == union(T2.path.parent_concept_ids)</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="44" customHeight="1">
@@ -11983,10 +11983,10 @@
         <x:v>PROFILE_ATTRIBUTION_AND_Q08</x:v>
       </x:c>
       <x:c r="D12" t="str">
-        <x:v>增加主要画像能力字段；统一L0—L3锚点；Q08题面复述不再构成能力证据。</x:v>
+        <x:v>增加主要画像能力字段；统一L0—L3锚点；隔离Q08题面复述；校正Q07—Q10跨表能力映射与Q10规则反馈证据。</x:v>
       </x:c>
       <x:c r="E12" t="str">
-        <x:v>防止一条表达重复进入多个画像维度，并隔离题面已给信息造成的虚假能力证据。</x:v>
+        <x:v>防止一条表达重复或错位进入画像维度，并隔离题面已给信息造成的虚假能力证据。</x:v>
       </x:c>
       <x:c r="F12" t="str">
         <x:v>项目负责人确认；模拟试验启用</x:v>
